--- a/margin_repository/Business_Rule_Register.xlsx
+++ b/margin_repository/Business_Rule_Register.xlsx
@@ -10,9 +10,7 @@
     <sheet name="Business_Rules" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Business_Rules'!$A$1:$J$21</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,7 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <sz val="9"/>
@@ -63,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E9C6"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,27 +79,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -477,19 +470,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +495,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Business Area</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -510,35 +505,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Current System Behavior</t>
+          <t>Decision Required</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Proposed Production Behavior</t>
+          <t>Proposed Option</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Pilot Evidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Business Owner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Finance Owner</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Decision Status</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Final Decision</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Approval Status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Approval Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -547,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -557,37 +562,51 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EAN is the primary article identifier across all chains</t>
+          <t>EAN is the primary article identifier within each chain</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EAN-priority key: Chain+EAN+PackSize+MRP. When EAN present, it dominates article identity.</t>
+          <t>Confirm EAN-priority key: Chain+EAN+PackSize+MRP</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Same — EAN always primary. Fallback used only when EAN is genuinely blank.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>Use EAN; fallback to Chain+Brand+Article+PackSize+MRP when blank</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 66/67 rows used EAN key; 1 blank-EAN used fallback (correctly flagged)</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Business team to confirm: Is EAN always the primary identity? Any chain that uses Article code instead?</t>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>EAN-priority with flagged fallback</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Pilot evidence confirms correct behavior</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BR-002</t>
+          <t>BR-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -597,197 +616,267 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fallback identity when EAN is blank</t>
+          <t>Blank EAN triggers a fallback key and a WARNING flag</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Fallback key: Chain+Brand+Article+PackSize+MRP. Record flagged BLANK_EAN (WARNING).</t>
+          <t>Allow fallback key or block the record?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Same — fallback key used, article flagged. Business should aim to fill EAN for all articles.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>Allow with WARNING flag; fallback key is ALT|Chain+Brand+Article+PackSize+MRP</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 blank-EAN record correctly flagged BLANK_EAN, used ALT| key, status=PUBLISHED</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Confirm fallback combination. Should BLANK_EAN be WARNING or FAIL?</t>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Allow with WARNING</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed in pilot — record remains publishable</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BR-003</t>
+          <t>BR-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Handling</t>
+          <t>Duplicate Detection</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Duplicate EAN within same chain flagged</t>
+          <t>Same Chain+Article+EffectiveDate creates a DUPLICATE_EFFECTIVE_DATE flag</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>DUPLICATE_EAN flag (WARNING) when same Chain+EAN maps to &gt;1 distinct Article name.</t>
+          <t>Block or warn on duplicate effective dates?</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Same — flag and surface for review. Do not auto-merge.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>FAIL — hold from forecast until resolved</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: DUPLICATE_CHAIN_ARTICLE flagged on 3 records; DUPLICATE_EAN on 4 records</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Should duplicate EAN block the record or just warn?</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL for same effective date; WARN for same article name</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Severity configurable in config.py</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-04</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Handling</t>
+          <t>Margin Definition</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Chain+Article flagged</t>
+          <t>Final Effective Margin % derived from signed commercial components when source is blank</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>DUPLICATE_CHAIN_ARTICLE flag (WARNING) when same Chain+Article appears multiple times.</t>
+          <t>Accept derived margin or require explicit Final Margin from source?</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Same — warn. Multiple rows may represent different pack sizes or effective dates.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
+          <t>Derive when blank; respect source value when provided</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: All 67 rows had derived FEM computed = sum of signed components</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Confirm: same Chain+Article with different Pack Size/MRP is valid, not a duplicate.</t>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Derive when blank; accept source when provided</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Component signs configurable in schema.py</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BR-005</t>
+          <t>BR-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Duplicate Handling</t>
+          <t>Margin Validation</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Duplicate effective date for same article identity</t>
+          <t>Margin above 100% or below 0% is BLOCKED</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DUPLICATE_EFFECTIVE_DATE flag (FAIL) when same identity+date appears multiple times.</t>
+          <t>Confirm absolute margin bounds</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Same — FAIL severity, held from forecast until resolved.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
+          <t>BLOCKED: margin &gt;100% or &lt;0% requires manual review</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record at 120% TM → BLOCKED (MARGIN_OVER_100); 1 at -5% TM → BLOCKED (NEGATIVE_MARGIN)</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Should duplicate effective dates be FAIL or BLOCKED?</t>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED for out-of-bounds margins</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Bounds configurable in config.py margin_bounds</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Margin Hierarchy</t>
+          <t>GST Validation</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Final Effective Margin % priority</t>
+          <t>GST must be in the valid set {0, 5, 12, 18, 28}</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Source-provided Final Effective Margin % is respected. When blank, computed from components: sum of earned margins minus Consumer Offer % and Cash Discount %.</t>
+          <t>What severity for incorrect GST?</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Same — provided value always wins. Derivation only fills blanks.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>FAIL — hold record; BLOCKED for unsupported rates</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with GST=15% → FAIL (INCORRECT_GST), correctly held</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Confirm: which margin field has priority when source provides multiple?</t>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>FAIL for invalid GST; BLOCKED for unsupported</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>GST controls configurable in config.py</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BR-007</t>
+          <t>BR-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -797,555 +886,710 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Invalid GST handling</t>
+          <t>Blank GST generates a WARNING</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>GST not in {0, 5, 12, 18, 28} triggers INCORRECT_GST flag with FAIL severity.</t>
+          <t>Warn or block on blank GST?</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Same — FAIL severity. Record held from forecast until GST corrected.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>WARNING — investigate but allow publish if GST not required for calculation</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with blank GST → WARNING (BLANK_GST), status=PUBLISHED</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Should invalid GST block the record (BLOCKED) or only FAIL?</t>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>WARNING for blank GST</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Severity configurable</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>BR-008</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Margin Limits</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Margin &gt; 100% handling</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>MARGIN_OVER_100 flag with BLOCKED severity. Record excluded from forecast.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Same — BLOCKED. A margin &gt;100% is always a data error.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BR-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Missing Data</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Missing Chain → BLOCKED; Missing Brand → FAIL; Missing Category → FAIL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Confirm severity for missing mandatory fields</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Chain=BLOCKED (cannot identify article without chain); Brand/Category=FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 blank chain → BLOCKED; 1 blank brand → FAIL; 1 blank category → FAIL</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Chain=BLOCKED; Brand=FAIL; Category=FAIL</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Standard business rule — margin cannot exceed 100%.</t>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>All correctly classified in pilot</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BR-009</t>
+          <t>BR-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Margin Limits</t>
+          <t>Versioning</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Negative margin handling</t>
+          <t>Changed articles get a new version; unchanged articles do NOT</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NEGATIVE_MARGIN flag with BLOCKED severity. Record excluded from forecast.</t>
+          <t>Confirm append-only versioning behavior</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Same — BLOCKED. Negative margins need explicit business review.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>New version only when tracked field changes; unchanged = skip (no duplicate)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Pilot batch 2: 5 changed → v2 (14 field changes logged); 8 unchanged → no new version</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Some chains may have negative margins during promotions. Confirm if BLOCKED is correct.</t>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Version on change only; never duplicate unchanged</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Verified with 2-batch pilot</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BR-010</t>
+          <t>BR-10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Listing Status</t>
+          <t>Forecast Eligibility</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Delisted articles remain searchable</t>
+          <t>Only APPROVED + Active + PASS/WARNING records are forecast-eligible</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INACTIVE_ARTICLE flag (WARNING). Record stays in history and current view but flagged.</t>
+          <t>Confirm forecast-ready filter criteria</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Same — delisted articles visible with flag. Not included in forecast-ready output.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>Record_Status=PUBLISHED (PASS or WARNING severity); HELD records excluded</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 60/67 published in batch 1; 7 HELD (3 FAIL + 4 BLOCKED)</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Should delisted articles be included in current view or only history?</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>PUBLISHED = forecast-eligible; HELD = excluded</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BR-011</t>
+          <t>BR-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Effective Dates</t>
+          <t>Commercials</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Historical and future margins can coexist</t>
+          <t>All commercial components zero/blank → MISSING_COMMERCIALS warning</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Both accepted. Future Effective From dates create a scheduled version. Expired Effective To dates trigger EXPIRED_COMMERCIAL (WARNING).</t>
+          <t>Warn or block when no commercials provided?</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Same — coexistence allowed. Business reviews future-effective margins before activation.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>WARNING — flag for review but don't block</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with all zeros → WARNING (MISSING_COMMERCIALS), PUBLISHED</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Confirm: can historical and future margins coexist for the same article?</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WARNING for missing commercials</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Forecast Eligibility</t>
+          <t>Listing Status</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Which statuses feed demand planning</t>
+          <t>Inactive/Delisted/Discontinued articles are flagged INACTIVE_ARTICLE</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Only PUBLISHED records (PASS or WARNING severity) with Status=ACTIVE included in Sheet 7 (Forecast-Ready) and Sheet 8 (CM2-Ready).</t>
+          <t>Warn or block inactive articles?</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Only APPROVED + ACTIVE + PUBLISHED records should feed forecast.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>WARNING — retain history but flag; exclude from forecast consideration</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 Delisted record → WARNING (INACTIVE_ARTICLE), PUBLISHED</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Confirm: APPROVED + ACTIVE + PUBLISHED = forecast-eligible.</t>
-        </is>
-      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WARNING — keep but flag</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Approval Workflow</t>
+          <t>Date Validation</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Who can approve or reject margin changes</t>
+          <t>Expired Effective To date generates EXPIRED_COMMERCIAL warning</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Approval_Status field populated from source file. No enforced workflow yet.</t>
+          <t>Warn or block expired commercials?</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>DRAFT → PENDING_REVIEW → APPROVED/REJECTED. Only APPROVED enters production.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>WARNING — flag for review; do not block historical records</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with Effective To=2026-01-31 → WARNING (EXPIRED_COMMERCIAL)</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Define approval authority matrix: who submits, who reviews, who approves.</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WARNING for expired commercials</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BR-014</t>
+          <t>BR-14</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Impact Calculation</t>
+          <t>Pack Size</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Impact driver for rupee impact</t>
+          <t>Blank pack size generates INCORRECT_PACK_SIZE warning</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Monthly_NSV from optional drivers frame. When absent, only percentage-point delta reported. Rupee impact = NSV × margin delta / 100.</t>
+          <t>Warn or block blank pack size?</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Same — NSV is the primary driver. Never fabricate when absent.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>WARNING — pack size useful but not critical for margin calculation</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with blank pack size → WARNING (INCORRECT_PACK_SIZE)</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>PENDING_APPROVAL</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Confirm: NSV, MRP sales, units, or forecast volume as impact driver?</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WARNING for blank pack size</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>BR-015</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Missing Data</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Blank MRP handling</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_MRP flag with BLOCKED severity. Record cannot be published.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Same — MRP is essential for article identity and commercial calculations.</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BR-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Trade Margin</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Blank Trade Margin generates BLANK_TRADE_MARGIN warning</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Warn or block blank trade margin?</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>WARNING — record may still have valid Final Effective Margin from other components</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with blank TM → WARNING (BLANK_TRADE_MARGIN)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WARNING for blank trade margin</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>MRP is a key field — blank MRP always blocks.</t>
-        </is>
-      </c>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>BR-016</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Missing Data</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Missing Chain handling</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>MISSING_CHAIN flag with BLOCKED severity.</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Same — Chain is mandatory for all repository operations.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BR-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Blank MRP → BLOCKED (cannot compute margin economics without MRP)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Confirm MRP is mandatory</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED — MRP is essential for margin and pricing calculations</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: 1 record with blank MRP → BLOCKED (BLANK_MRP), correctly HELD</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED for blank MRP</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Chain is part of the primary key.</t>
-        </is>
-      </c>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>BR-017</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Version Control</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Append-only versioning</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Every change creates a new version. Previous versions are never overwritten or deleted. UNCHANGED rows are not re-stored (no false versions).</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Same — non-negotiable. Full audit trail preserved.</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BR-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Rollback restores repository to any prior snapshot; creates pre-rollback backup</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Confirm rollback behavior</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Non-destructive: archive current state before restoring; bidirectional restore supported</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: Rolled back to batch 1 (67 rows), pre-rollback snapshot auto-created, restored to batch 2 (74 rows)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Rollback with automatic pre-rollback backup</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Core non-negotiable from the charter.</t>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Verified bidirectional rollback in pilot</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BR-018</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Rollback</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Rollback archives current state before restoring</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Pre-rollback snapshot created automatically. Original state recoverable.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Same — rollback is non-destructive.</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BR-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Source rows must equal New + Changed + Unchanged (diff must be 0)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Confirm reconciliation control</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation diff is computed and checked on every import</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: Batch 1 (67=67+0+0, diff=0) + Batch 2 (15=2+5+8, diff=0) — both PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory zero-diff reconciliation on every import</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Safety net for any rollback operation.</t>
-        </is>
-      </c>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Impact Analysis</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>High-risk margin change threshold</t>
+          <t>Margin changes classified into risk tiers: NORMAL/WARNING/HIGH_RISK/BLOCKED</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Margin change &gt;= 2.0 percentage points flagged as HIGH RISK in impact analysis.</t>
+          <t>Confirm risk tier thresholds</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Same — configurable threshold (currently 2.0 pp).</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>±1pp=NORMAL, ±3pp=WARNING, ±5pp=HIGH_RISK, &gt;5pp=BLOCKED</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Pilot batch 2: 14 changelog entries with diffs from -6pp to +6pp</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Thresholds configurable; defaults reasonable for pilot</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>PENDING_APPROVAL</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the high-risk threshold. Should it be 2pp, 3pp, or different by category?</t>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Business/Finance must confirm final thresholds</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>BR-020</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Data Integrity</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Leading zeroes in EAN/Site Code</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>EAN and SKU Code treated as text. Leading zeroes preserved.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Same — never convert to numeric.</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>APPROVED_BY_DEFAULT</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>EAN/barcode must retain leading zeroes.</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BR-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GST Cross-check</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GST mismatch with article master → BLOCKED; GST change from prior → WARNING</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Confirm GST cross-validation severity</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKED for mismatch with master; WARNING for change from prior version</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Pilot: GST controls configured and tested; no article master cross-check yet</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Requires integration with Article Master/Tax Master</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>PENDING_APPROVAL</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Awaiting Article Master integration + Finance/Tax sign-off</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1356,75 +1600,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Business Rule Register Summary</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Business Rule Register — Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Total Rules</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Total rules</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Approved / Default</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED_BY_PILOT</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Pending Approval</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>PENDING_APPROVAL</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PASS WITH WARNINGS</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Pending rules:</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>14 rules require business team sign-off before production deployment.</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>BR-19</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Risk tier thresholds — awaiting Finance/Commercial confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>BR-20</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>GST cross-check with Article Master — awaiting integration</t>
         </is>
       </c>
     </row>
